--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:25:22+00:00</t>
+    <t>2025-07-07T15:26:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3824" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4183" uniqueCount="557">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T15:26:46+00:00</t>
+    <t>2025-10-08T07:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1028,6 +1028,213 @@
   </si>
   <si>
     <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
+  </si>
+  <si>
+    <t>Practitioner.name.id</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension:assemblyOrder</t>
+  </si>
+  <si>
+    <t>assemblyOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.3.0-ballot-tc1}
+</t>
+  </si>
+  <si>
+    <t>Preferred display order of name parts</t>
+  </si>
+  <si>
+    <t>A code that represents the preferred display order of the components of this human name.</t>
+  </si>
+  <si>
+    <t>Practitioner.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Practitioner.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>./FamilyName</t>
+  </si>
+  <si>
+    <t>Practitioner.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>./GivenNames</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>./TitleCode</t>
+  </si>
+  <si>
+    <t>Practitioner.name.suffix</t>
+  </si>
+  <si>
+    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>Civilités d'exercice d'un professionnel du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>Practitioner.name.period</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
   </si>
   <si>
     <t>Practitioner.telecom</t>
@@ -1848,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN105"/>
+  <dimension ref="A1:AN115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.98046875" customWidth="true" bestFit="true"/>
@@ -1886,7 +2093,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.16015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -7506,7 +7713,7 @@
         <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>78</v>
@@ -7515,23 +7722,19 @@
         <v>78</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>323</v>
+        <v>103</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>324</v>
+        <v>104</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
       </c>
@@ -7579,28 +7782,28 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>106</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>330</v>
+        <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>78</v>
@@ -7608,14 +7811,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7631,23 +7834,21 @@
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>332</v>
+        <v>110</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>333</v>
+        <v>111</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>334</v>
+        <v>112</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -7683,19 +7884,19 @@
         <v>78</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>331</v>
+        <v>117</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7707,16 +7908,16 @@
         <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>337</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -7724,12 +7925,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="D52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7747,21 +7950,19 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>169</v>
+        <v>326</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="N52" s="2"/>
-      <c r="O52" t="s" s="2">
-        <v>343</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
       </c>
@@ -7785,13 +7986,13 @@
         <v>78</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -7809,28 +8010,28 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>340</v>
+        <v>117</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -7838,10 +8039,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7858,23 +8059,25 @@
         <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>350</v>
+        <v>169</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7899,13 +8102,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -7923,7 +8126,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7938,13 +8141,13 @@
         <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
@@ -7952,10 +8155,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7966,7 +8169,7 @@
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -7975,20 +8178,22 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>358</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
@@ -8037,13 +8242,13 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
@@ -8052,13 +8257,13 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8066,21 +8271,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -8089,18 +8294,20 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>365</v>
+        <v>103</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8137,23 +8344,25 @@
         <v>78</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AC55" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
@@ -8162,13 +8371,13 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -8176,21 +8385,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>358</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -8199,18 +8408,20 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>104</v>
+        <v>359</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8259,28 +8470,28 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>106</v>
+        <v>362</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>363</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>107</v>
+        <v>364</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8288,21 +8499,21 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>78</v>
@@ -8311,20 +8522,18 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -8349,13 +8558,13 @@
         <v>78</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>78</v>
+        <v>369</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8373,7 +8582,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>117</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8385,16 +8594,16 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>107</v>
+        <v>373</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -8402,14 +8611,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8422,13 +8631,13 @@
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>376</v>
@@ -8436,12 +8645,8 @@
       <c r="M58" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8465,13 +8670,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -8489,7 +8694,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8501,13 +8706,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>78</v>
+        <v>381</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>192</v>
+        <v>382</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8518,10 +8723,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8532,7 +8737,7 @@
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>78</v>
@@ -8541,20 +8746,20 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8603,13 +8808,13 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
@@ -8618,13 +8823,13 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -8632,10 +8837,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8643,10 +8848,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8655,19 +8860,23 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>232</v>
+        <v>391</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>395</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -8691,13 +8900,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8715,13 +8924,13 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
@@ -8730,13 +8939,13 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -8744,10 +8953,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8758,7 +8967,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -8767,20 +8976,22 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>260</v>
+        <v>400</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -8829,13 +9040,13 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
@@ -8844,13 +9055,13 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>78</v>
+        <v>405</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -8858,10 +9069,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8881,19 +9092,21 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -8917,13 +9130,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>412</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -8941,7 +9154,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8956,13 +9169,13 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>78</v>
+        <v>414</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -8970,14 +9183,12 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>78</v>
       </c>
@@ -8986,7 +9197,7 @@
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -8995,19 +9206,21 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9055,13 +9268,13 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
@@ -9070,13 +9283,13 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9084,10 +9297,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9098,7 +9311,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9110,16 +9323,18 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>426</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>104</v>
+        <v>427</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>105</v>
+        <v>428</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9167,28 +9382,28 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>106</v>
+        <v>425</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>107</v>
+        <v>430</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9196,14 +9411,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>404</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9222,17 +9437,15 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>110</v>
+        <v>433</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>111</v>
+        <v>434</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
@@ -9269,19 +9482,17 @@
         <v>78</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="AC65" s="2"/>
       <c r="AD65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>117</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9293,16 +9504,16 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>78</v>
+        <v>437</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9310,46 +9521,42 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>104</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9397,25 +9604,25 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>378</v>
+        <v>106</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9426,14 +9633,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>406</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>379</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9452,18 +9659,18 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>209</v>
+        <v>110</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>380</v>
+        <v>111</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
@@ -9511,7 +9718,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>379</v>
+        <v>117</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9523,13 +9730,13 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>383</v>
+        <v>107</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
@@ -9540,42 +9747,46 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>384</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>385</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9599,13 +9810,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9623,28 +9834,28 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>384</v>
+        <v>446</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>370</v>
+        <v>192</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -9652,10 +9863,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>408</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9666,7 +9877,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -9678,16 +9889,18 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>104</v>
+        <v>448</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>105</v>
+        <v>449</v>
       </c>
       <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9735,25 +9948,25 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>106</v>
+        <v>447</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>107</v>
+        <v>451</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
@@ -9764,21 +9977,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>410</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -9790,17 +10003,15 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>111</v>
+        <v>453</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -9825,52 +10036,52 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>117</v>
+        <v>452</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -9878,10 +10089,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>412</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9892,7 +10103,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -9901,22 +10112,20 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -9953,23 +10162,25 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
@@ -9978,13 +10189,13 @@
         <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -9992,14 +10203,12 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10017,23 +10226,19 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>414</v>
+        <v>465</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10057,11 +10262,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10079,13 +10286,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10094,10 +10301,10 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10108,13 +10315,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>425</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>401</v>
+        <v>469</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>78</v>
@@ -10124,7 +10331,7 @@
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10133,23 +10340,19 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10173,11 +10376,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>426</v>
+        <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10195,7 +10400,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10210,13 +10415,13 @@
         <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10224,10 +10429,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10247,23 +10452,19 @@
         <v>78</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10311,7 +10512,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10323,13 +10524,13 @@
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
@@ -10340,21 +10541,21 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10366,18 +10567,18 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
@@ -10425,28 +10626,28 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -10454,42 +10655,46 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10537,25 +10742,25 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
@@ -10566,14 +10771,12 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>438</v>
+        <v>474</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10582,7 +10785,7 @@
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -10594,16 +10797,18 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -10651,7 +10856,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>364</v>
+        <v>447</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -10666,13 +10871,13 @@
         <v>101</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>370</v>
+        <v>451</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -10680,10 +10885,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>441</v>
+        <v>475</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>372</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10691,7 +10896,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -10706,13 +10911,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>453</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
+        <v>454</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10739,13 +10944,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -10763,10 +10968,10 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>452</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>89</v>
@@ -10775,16 +10980,16 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -10792,21 +10997,21 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>373</v>
+        <v>477</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -10818,17 +11023,15 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -10877,19 +11080,19 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -10906,14 +11109,14 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>374</v>
+        <v>479</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>375</v>
+        <v>109</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -10926,26 +11129,24 @@
         <v>78</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>376</v>
+        <v>111</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>377</v>
+        <v>112</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -10981,19 +11182,19 @@
         <v>78</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>378</v>
+        <v>117</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11011,7 +11212,7 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
@@ -11022,10 +11223,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>444</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>379</v>
+        <v>481</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11045,20 +11246,22 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O81" t="s" s="2">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11095,19 +11298,17 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC81" s="2"/>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11122,10 +11323,10 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11136,18 +11337,20 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>445</v>
+        <v>490</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>89</v>
@@ -11159,19 +11362,23 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>385</v>
+        <v>482</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11195,13 +11402,11 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11219,13 +11424,13 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
@@ -11234,13 +11439,13 @@
         <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11248,12 +11453,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11271,19 +11478,23 @@
         <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>104</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11307,13 +11518,11 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11331,25 +11540,25 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>106</v>
+        <v>487</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11360,21 +11569,21 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>447</v>
+        <v>495</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>411</v>
+        <v>496</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -11383,21 +11592,23 @@
         <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>111</v>
+        <v>497</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>112</v>
+        <v>498</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11433,37 +11644,37 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>107</v>
+        <v>503</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
@@ -11474,10 +11685,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>448</v>
+        <v>504</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11488,7 +11699,7 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -11497,22 +11708,20 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
@@ -11549,23 +11758,25 @@
         <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
@@ -11574,13 +11785,13 @@
         <v>101</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -11588,14 +11799,12 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11613,23 +11822,19 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
       </c>
@@ -11653,11 +11858,13 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -11675,13 +11882,13 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
@@ -11690,10 +11897,10 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
@@ -11704,13 +11911,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>453</v>
+        <v>506</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
@@ -11729,23 +11936,19 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -11769,11 +11972,13 @@
         <v>78</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -11791,7 +11996,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -11806,13 +12011,13 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -11820,10 +12025,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11843,23 +12048,19 @@
         <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -11907,7 +12108,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -11919,13 +12120,13 @@
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -11936,21 +12137,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>458</v>
+        <v>510</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -11962,18 +12163,18 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
       </c>
@@ -12021,28 +12222,28 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12050,42 +12251,46 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>459</v>
+        <v>511</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12133,25 +12338,25 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>78</v>
@@ -12162,14 +12367,12 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>460</v>
+        <v>512</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12190,16 +12393,18 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12247,7 +12452,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>364</v>
+        <v>447</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12262,13 +12467,13 @@
         <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>370</v>
+        <v>451</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>371</v>
+        <v>78</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12276,10 +12481,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>463</v>
+        <v>513</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>372</v>
+        <v>452</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12287,7 +12492,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>89</v>
@@ -12302,13 +12507,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>104</v>
+        <v>453</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>105</v>
+        <v>454</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12335,13 +12540,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12359,10 +12564,10 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>106</v>
+        <v>452</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>89</v>
@@ -12371,16 +12576,16 @@
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -12388,21 +12593,21 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>464</v>
+        <v>514</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>373</v>
+        <v>477</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12414,17 +12619,15 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -12473,19 +12676,19 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -12502,14 +12705,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>465</v>
+        <v>515</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>374</v>
+        <v>479</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>375</v>
+        <v>109</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12522,26 +12725,24 @@
         <v>78</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>376</v>
+        <v>111</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>377</v>
+        <v>112</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O94" t="s" s="2">
-        <v>206</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -12577,19 +12778,19 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>378</v>
+        <v>117</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -12607,7 +12808,7 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
@@ -12618,10 +12819,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>466</v>
+        <v>516</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>379</v>
+        <v>481</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12641,20 +12842,22 @@
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>209</v>
+        <v>147</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O95" t="s" s="2">
-        <v>382</v>
+        <v>485</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -12691,19 +12894,17 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC95" s="2"/>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>78</v>
+        <v>486</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>379</v>
+        <v>487</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -12718,10 +12919,10 @@
         <v>101</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>383</v>
+        <v>489</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
@@ -12732,18 +12933,20 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>467</v>
+        <v>517</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="C96" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="D96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>89</v>
@@ -12755,19 +12958,23 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>385</v>
+        <v>519</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -12791,13 +12998,11 @@
         <v>78</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y96" s="2"/>
       <c r="Z96" t="s" s="2">
-        <v>388</v>
+        <v>520</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>78</v>
@@ -12815,13 +13020,13 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
@@ -12830,13 +13035,13 @@
         <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>370</v>
+        <v>489</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -12844,12 +13049,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>468</v>
+        <v>521</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>522</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
@@ -12867,19 +13074,23 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>104</v>
+        <v>523</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
       </c>
@@ -12903,13 +13114,11 @@
         <v>78</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>78</v>
+        <v>524</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -12927,25 +13136,25 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>106</v>
+        <v>487</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>78</v>
+        <v>488</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>107</v>
+        <v>489</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -12956,21 +13165,21 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>411</v>
+        <v>496</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -12979,21 +13188,23 @@
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>111</v>
+        <v>497</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>112</v>
+        <v>498</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
       </c>
@@ -13029,37 +13240,37 @@
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>78</v>
+        <v>502</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>107</v>
+        <v>503</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
@@ -13070,10 +13281,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>413</v>
+        <v>458</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13084,7 +13295,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13093,22 +13304,20 @@
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>414</v>
+        <v>459</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>417</v>
+        <v>461</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13145,23 +13354,25 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AC99" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
@@ -13170,13 +13381,13 @@
         <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13184,14 +13395,12 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>471</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C100" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13209,23 +13418,19 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -13249,11 +13454,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>474</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13271,13 +13478,13 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>419</v>
+        <v>464</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13286,10 +13493,10 @@
         <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>78</v>
@@ -13300,13 +13507,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>475</v>
+        <v>528</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>78</v>
@@ -13316,7 +13523,7 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -13325,23 +13532,19 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>476</v>
+        <v>530</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
@@ -13365,11 +13568,13 @@
         <v>78</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13387,7 +13592,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13402,13 +13607,13 @@
         <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -13416,10 +13621,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>478</v>
+        <v>531</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13439,23 +13644,19 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>429</v>
+        <v>104</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -13503,7 +13704,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>433</v>
+        <v>106</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13515,13 +13716,13 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>435</v>
+        <v>107</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>78</v>
@@ -13532,21 +13733,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -13558,18 +13759,18 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
       </c>
@@ -13617,28 +13818,28 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>394</v>
+        <v>107</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -13646,42 +13847,46 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>268</v>
+        <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
@@ -13729,25 +13934,25 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>399</v>
+        <v>192</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>78</v>
@@ -13758,10 +13963,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>481</v>
+        <v>534</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13784,19 +13989,17 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>482</v>
+        <v>448</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>485</v>
+        <v>450</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -13821,13 +14024,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -13845,7 +14048,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -13860,15 +14063,1157 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AC109" s="2"/>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AL105" t="s" s="2">
+      <c r="AF109" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK109" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AN105" t="s" s="2">
+      <c r="AL109" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="D110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y110" s="2"/>
+      <c r="Z110" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="P111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y111" s="2"/>
+      <c r="Z111" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="P112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AN115" t="s" s="2">
         <v>78</v>
       </c>
     </row>

--- a/nr-update-change-notes/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-update-change-notes/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:41:56+00:00</t>
+    <t>2025-10-08T15:42:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
